--- a/tools/excel/anssi/nis2/recyf.xlsx
+++ b/tools/excel/anssi/nis2/recyf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\anssi\nis2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abder/mydev/intuitem/staging/ciso-assistant-community/tools/excel/anssi/nis2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22C18DD-3451-40F4-B588-98B92D41B05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180D68F7-0107-4B4C-86E7-DA4D2539A670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="852" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8240" yWindow="-24240" windowWidth="36820" windowHeight="19840" tabRatio="852" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -622,9 +622,6 @@
     <t>7.A.4</t>
   </si>
   <si>
-    <t>Les sous-systèmes identifiés à la mesure 7.A.4-EE sont cloisonnés entre eux physiquement et/ou logiquement.</t>
-  </si>
-  <si>
     <t>urn:intuitem:risk:function:doc-pol:pol.network,
 urn:intuitem:risk:function:doc-pol:tech.microsegmentation,
 urn:intuitem:risk:function:doc-pol:tech.vlan</t>
@@ -1941,6 +1938,9 @@
   </si>
   <si>
     <t>urn:intuitem:risk:function:doc-pol</t>
+  </si>
+  <si>
+    <t>Les sous-systèmes identifiés à la mesure 7.A.3-EE sont cloisonnés entre eux physiquement et/ou logiquement.</t>
   </si>
 </sst>
 </file>
@@ -2523,98 +2523,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105.77734375" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" t="s">
         <v>509</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>511</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>513</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>514</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>519</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>521</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>523</v>
       </c>
-      <c r="B10" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>524</v>
-      </c>
-      <c r="B11" t="s">
-        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -2625,66 +2625,66 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>528</v>
       </c>
-      <c r="B3" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
         <v>530</v>
-      </c>
-      <c r="B7" t="s">
-        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -2695,16 +2695,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G187"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" customWidth="1"/>
     <col min="4" max="4" width="46" style="1" customWidth="1"/>
     <col min="5" max="5" width="77.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.109375" customWidth="1"/>
-    <col min="7" max="7" width="57.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.1640625" customWidth="1"/>
+    <col min="7" max="7" width="57.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>1</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1</v>
       </c>
@@ -2809,7 +2809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>2</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>2</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="172.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="172.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="115.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>2</v>
       </c>
@@ -3002,7 +3002,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>1</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>2</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="158.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -3104,7 +3104,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>2</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>1</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -3206,7 +3206,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>1</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>2</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="144" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>2</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>9</v>
       </c>
@@ -3359,7 +3359,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="100.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>1</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52">
         <v>1</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B53">
         <v>2</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -3703,440 +3703,440 @@
         <v>158</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F57" t="s">
+        <v>29</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F57" t="s">
-        <v>29</v>
-      </c>
-      <c r="G57" s="1" t="s">
+    </row>
+    <row r="58" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58">
-        <v>3</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="E58" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="F58" t="s">
+        <v>29</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F58" t="s">
-        <v>29</v>
-      </c>
-      <c r="G58" s="1" t="s">
+    </row>
+    <row r="59" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59">
-        <v>3</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="E59" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" t="s">
+        <v>29</v>
+      </c>
+      <c r="G59" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F59" t="s">
-        <v>29</v>
-      </c>
-      <c r="G59" s="1" t="s">
+    </row>
+    <row r="60" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60">
-        <v>3</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="E60" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="1" t="s">
+    </row>
+    <row r="61" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="E61" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" t="s">
+        <v>29</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
         <v>171</v>
       </c>
-      <c r="F61" t="s">
-        <v>29</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D62" s="1" t="s">
+    </row>
+    <row r="63" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63">
-        <v>3</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="E63" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="F63" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F63" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="1" t="s">
+    </row>
+    <row r="64" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="E64" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" t="s">
+        <v>29</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
         <v>178</v>
       </c>
-      <c r="F64" t="s">
-        <v>29</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65">
-        <v>3</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="E65" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F65" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="1" t="s">
+    </row>
+    <row r="66" spans="1:7" ht="100.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="E66" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F66" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" s="1" t="s">
+    </row>
+    <row r="67" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="E67" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F67" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D68" s="1" t="s">
+    </row>
+    <row r="69" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="E69" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="F69" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="1" t="s">
+    </row>
+    <row r="70" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="E70" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F70" t="s">
-        <v>12</v>
-      </c>
-      <c r="G70" s="1" t="s">
+    </row>
+    <row r="71" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="E71" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F71" t="s">
-        <v>29</v>
-      </c>
-      <c r="G71" s="1" t="s">
+    </row>
+    <row r="72" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="E72" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F72" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="1" t="s">
+    </row>
+    <row r="73" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+      <c r="C73" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>9</v>
-      </c>
-      <c r="B73">
-        <v>2</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="E73" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F73" t="s">
-        <v>29</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D74" s="1" t="s">
+    </row>
+    <row r="75" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>9</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="E75" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="F75" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F75" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="1" t="s">
+    </row>
+    <row r="76" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="E76" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F76" t="s">
-        <v>29</v>
-      </c>
-      <c r="G76" s="1" t="s">
+    </row>
+    <row r="77" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>9</v>
-      </c>
-      <c r="B77">
-        <v>2</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="E77" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F77" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="1" t="s">
+    </row>
+    <row r="78" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+      <c r="C78" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>9</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="E78" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
         <v>217</v>
       </c>
-      <c r="F78" t="s">
-        <v>29</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>9</v>
-      </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="E79" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="F79" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F79" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="1" t="s">
+    </row>
+    <row r="80" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>9</v>
-      </c>
-      <c r="B80">
-        <v>2</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="E80" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -4145,7 +4145,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>9</v>
       </c>
@@ -4153,1992 +4153,1992 @@
         <v>2</v>
       </c>
       <c r="C81" t="s">
+        <v>222</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+      <c r="G81" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F81" t="s">
-        <v>12</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82" t="s">
+        <v>225</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D82" s="1" t="s">
+    </row>
+    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B83">
-        <v>2</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="D83" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D83" s="1" t="s">
+    </row>
+    <row r="84" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84">
-        <v>3</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="E84" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="F84" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" s="1" t="s">
+    </row>
+    <row r="85" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>9</v>
-      </c>
-      <c r="B85">
-        <v>3</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="E85" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="F85" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F85" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="1" t="s">
+    </row>
+    <row r="86" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86">
+        <v>3</v>
+      </c>
+      <c r="C86" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>9</v>
-      </c>
-      <c r="B86">
-        <v>3</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="E86" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="F86" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F86" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" s="1" t="s">
+    </row>
+    <row r="87" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87">
+        <v>3</v>
+      </c>
+      <c r="C87" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B87">
-        <v>3</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="E87" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
         <v>240</v>
       </c>
-      <c r="F87" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>9</v>
-      </c>
-      <c r="B88">
-        <v>3</v>
-      </c>
-      <c r="C88" t="s">
+      <c r="E88" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F88" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="1" t="s">
+    </row>
+    <row r="89" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89">
+        <v>3</v>
+      </c>
+      <c r="C89" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>9</v>
-      </c>
-      <c r="B89">
-        <v>3</v>
-      </c>
-      <c r="C89" t="s">
+      <c r="E89" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="F89" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F89" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="1" t="s">
+    </row>
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B90">
+        <v>2</v>
+      </c>
+      <c r="C90" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B90">
-        <v>2</v>
-      </c>
-      <c r="C90" t="s">
+      <c r="D90" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D90" s="1" t="s">
+    </row>
+    <row r="91" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91">
+        <v>3</v>
+      </c>
+      <c r="C91" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>9</v>
-      </c>
-      <c r="B91">
-        <v>3</v>
-      </c>
-      <c r="C91" t="s">
+      <c r="E91" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92" t="s">
         <v>250</v>
       </c>
-      <c r="F91" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>9</v>
-      </c>
-      <c r="B92">
-        <v>3</v>
-      </c>
-      <c r="C92" t="s">
+      <c r="E92" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F92" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>9</v>
-      </c>
-      <c r="B93">
-        <v>3</v>
-      </c>
-      <c r="C93" t="s">
+      <c r="E93" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94">
+        <v>3</v>
+      </c>
+      <c r="C94" t="s">
         <v>255</v>
       </c>
-      <c r="F93" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94">
-        <v>3</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="E94" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F94" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" s="1" t="s">
+    </row>
+    <row r="95" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95">
+        <v>3</v>
+      </c>
+      <c r="C95" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>9</v>
-      </c>
-      <c r="B95">
-        <v>3</v>
-      </c>
-      <c r="C95" t="s">
+      <c r="E95" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96" t="s">
         <v>260</v>
       </c>
-      <c r="F95" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B96">
-        <v>3</v>
-      </c>
-      <c r="C96" t="s">
+      <c r="E96" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="E96" s="1" t="s">
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
         <v>262</v>
       </c>
-      <c r="F96" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>9</v>
-      </c>
-      <c r="B97">
-        <v>3</v>
-      </c>
-      <c r="C97" t="s">
+      <c r="E97" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="F97" t="s">
+        <v>29</v>
+      </c>
+      <c r="G97" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F97" t="s">
-        <v>29</v>
-      </c>
-      <c r="G97" s="1" t="s">
+    </row>
+    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B98">
+        <v>2</v>
+      </c>
+      <c r="C98" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B98">
-        <v>2</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="D98" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D98" s="1" t="s">
+    </row>
+    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99">
+        <v>3</v>
+      </c>
+      <c r="C99" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>9</v>
-      </c>
-      <c r="B99">
-        <v>3</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="E99" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
         <v>269</v>
       </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>9</v>
-      </c>
-      <c r="B100">
-        <v>3</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="E100" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F100" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="1" t="s">
+    </row>
+    <row r="101" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101">
+        <v>3</v>
+      </c>
+      <c r="C101" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>9</v>
-      </c>
-      <c r="B101">
-        <v>3</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="E101" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102">
+        <v>3</v>
+      </c>
+      <c r="C102" t="s">
         <v>274</v>
       </c>
-      <c r="F101" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>9</v>
-      </c>
-      <c r="B102">
-        <v>3</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="E102" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="F102" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103" t="s">
+        <v>276</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D103" s="1" t="s">
+    </row>
+    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B104">
-        <v>2</v>
-      </c>
-      <c r="C104" t="s">
+      <c r="D104" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D104" s="1" t="s">
+    </row>
+    <row r="105" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105">
+        <v>3</v>
+      </c>
+      <c r="C105" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>9</v>
-      </c>
-      <c r="B105">
-        <v>3</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="E105" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="F105" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F105" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="1" t="s">
+    </row>
+    <row r="106" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106">
+        <v>3</v>
+      </c>
+      <c r="C106" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>9</v>
-      </c>
-      <c r="B106">
-        <v>3</v>
-      </c>
-      <c r="C106" t="s">
+      <c r="E106" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F106" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="1" t="s">
+    </row>
+    <row r="107" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107">
+        <v>3</v>
+      </c>
+      <c r="C107" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>9</v>
-      </c>
-      <c r="B107">
-        <v>3</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="E107" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
         <v>288</v>
       </c>
-      <c r="F107" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>9</v>
-      </c>
-      <c r="B108">
-        <v>3</v>
-      </c>
-      <c r="C108" t="s">
+      <c r="E108" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="F108" t="s">
+        <v>29</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
         <v>290</v>
       </c>
-      <c r="F108" t="s">
-        <v>29</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>9</v>
-      </c>
-      <c r="B109">
-        <v>3</v>
-      </c>
-      <c r="C109" t="s">
+      <c r="E109" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F109" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" s="1" t="s">
+    </row>
+    <row r="110" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110">
+        <v>3</v>
+      </c>
+      <c r="C110" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>9</v>
-      </c>
-      <c r="B110">
-        <v>3</v>
-      </c>
-      <c r="C110" t="s">
+      <c r="E110" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="F110" t="s">
+        <v>29</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="F110" t="s">
-        <v>29</v>
-      </c>
-      <c r="G110" s="1" t="s">
+    </row>
+    <row r="111" spans="1:7" ht="115.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111">
+        <v>3</v>
+      </c>
+      <c r="C111" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>9</v>
-      </c>
-      <c r="B111">
-        <v>3</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="E111" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="F111" t="s">
+        <v>29</v>
+      </c>
+      <c r="G111" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F111" t="s">
-        <v>29</v>
-      </c>
-      <c r="G111" s="1" t="s">
+    </row>
+    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B112">
-        <v>2</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="D112" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D112" s="1" t="s">
+    </row>
+    <row r="113" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>9</v>
-      </c>
-      <c r="B113">
-        <v>3</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="E113" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F113" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" s="1" t="s">
+    </row>
+    <row r="114" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114">
+        <v>3</v>
+      </c>
+      <c r="C114" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>9</v>
-      </c>
-      <c r="B114">
-        <v>3</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="E114" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="F114" t="s">
+        <v>29</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F114" t="s">
-        <v>29</v>
-      </c>
-      <c r="G114" s="1" t="s">
+    </row>
+    <row r="115" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>9</v>
-      </c>
-      <c r="B115">
-        <v>3</v>
-      </c>
-      <c r="C115" t="s">
+      <c r="E115" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="F115" t="s">
+        <v>29</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F115" t="s">
-        <v>29</v>
-      </c>
-      <c r="G115" s="1" t="s">
+    </row>
+    <row r="116" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>9</v>
-      </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116" t="s">
+      <c r="E116" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="F116" t="s">
+        <v>29</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F116" t="s">
-        <v>29</v>
-      </c>
-      <c r="G116" s="1" t="s">
+    </row>
+    <row r="117" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>9</v>
-      </c>
-      <c r="B117">
-        <v>3</v>
-      </c>
-      <c r="C117" t="s">
+      <c r="E117" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="F117" t="s">
+        <v>29</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F117" t="s">
-        <v>29</v>
-      </c>
-      <c r="G117" s="1" t="s">
+    </row>
+    <row r="118" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>9</v>
-      </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="E118" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="F118" t="s">
+        <v>29</v>
+      </c>
+      <c r="G118" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F118" t="s">
-        <v>29</v>
-      </c>
-      <c r="G118" s="1" t="s">
+    </row>
+    <row r="119" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119">
+        <v>3</v>
+      </c>
+      <c r="C119" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>9</v>
-      </c>
-      <c r="B119">
-        <v>3</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="E119" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="F119" t="s">
+        <v>29</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F119" t="s">
-        <v>29</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120" t="s">
+        <v>322</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D120" s="1" t="s">
+    </row>
+    <row r="121" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>9</v>
-      </c>
-      <c r="B121">
-        <v>2</v>
-      </c>
-      <c r="C121" t="s">
+      <c r="E121" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="F121" t="s">
+        <v>29</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="F121" t="s">
-        <v>29</v>
-      </c>
-      <c r="G121" s="1" t="s">
+    </row>
+    <row r="122" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122">
+        <v>2</v>
+      </c>
+      <c r="C122" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>9</v>
-      </c>
-      <c r="B122">
-        <v>2</v>
-      </c>
-      <c r="C122" t="s">
+      <c r="E122" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="F122" t="s">
+        <v>29</v>
+      </c>
+      <c r="G122" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="F122" t="s">
-        <v>29</v>
-      </c>
-      <c r="G122" s="1" t="s">
+    </row>
+    <row r="123" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>9</v>
-      </c>
-      <c r="B123">
-        <v>2</v>
-      </c>
-      <c r="C123" t="s">
+      <c r="E123" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="F123" t="s">
+        <v>12</v>
+      </c>
+      <c r="G123" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="F123" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="1" t="s">
+    </row>
+    <row r="124" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="C124" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>9</v>
-      </c>
-      <c r="B124">
-        <v>2</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="E124" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="F124" t="s">
+        <v>29</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F124" t="s">
-        <v>29</v>
-      </c>
-      <c r="G124" s="1" t="s">
+    </row>
+    <row r="125" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>9</v>
-      </c>
-      <c r="B125">
-        <v>2</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="E125" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="F125" t="s">
+        <v>29</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F125" t="s">
-        <v>29</v>
-      </c>
-      <c r="G125" s="1" t="s">
+    </row>
+    <row r="126" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>9</v>
-      </c>
-      <c r="B126">
-        <v>2</v>
-      </c>
-      <c r="C126" t="s">
+      <c r="E126" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="F126" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G126" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F126" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G126" s="1" t="s">
+    </row>
+    <row r="127" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>9</v>
-      </c>
-      <c r="B127">
-        <v>2</v>
-      </c>
-      <c r="C127" t="s">
+      <c r="E127" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="F127" t="s">
+        <v>29</v>
+      </c>
+      <c r="G127" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="F127" t="s">
-        <v>29</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128" t="s">
+        <v>345</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D128" s="1" t="s">
+    </row>
+    <row r="129" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>9</v>
-      </c>
-      <c r="B129">
-        <v>2</v>
-      </c>
-      <c r="C129" t="s">
+      <c r="E129" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="F129" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F129" t="s">
-        <v>12</v>
-      </c>
-      <c r="G129" s="1" t="s">
+    </row>
+    <row r="130" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130">
+        <v>2</v>
+      </c>
+      <c r="C130" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>9</v>
-      </c>
-      <c r="B130">
-        <v>2</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="E130" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="F130" t="s">
+        <v>12</v>
+      </c>
+      <c r="G130" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F130" t="s">
-        <v>12</v>
-      </c>
-      <c r="G130" s="1" t="s">
+    </row>
+    <row r="131" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>9</v>
-      </c>
-      <c r="B131">
-        <v>2</v>
-      </c>
-      <c r="C131" t="s">
+      <c r="E131" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="F131" t="s">
+        <v>12</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F131" t="s">
-        <v>12</v>
-      </c>
-      <c r="G131" s="1" t="s">
+    </row>
+    <row r="132" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132">
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>9</v>
-      </c>
-      <c r="B132">
-        <v>2</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="E132" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="F132" t="s">
+        <v>29</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F132" t="s">
-        <v>29</v>
-      </c>
-      <c r="G132" s="1" t="s">
+    </row>
+    <row r="133" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133">
+        <v>2</v>
+      </c>
+      <c r="C133" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>9</v>
-      </c>
-      <c r="B133">
-        <v>2</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="E133" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="F133" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G133" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="F133" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G133" s="1" t="s">
+    </row>
+    <row r="134" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>9</v>
-      </c>
-      <c r="B134">
-        <v>2</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="E134" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="F134" t="s">
+        <v>29</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="F134" t="s">
-        <v>29</v>
-      </c>
-      <c r="G134" s="1" t="s">
+    </row>
+    <row r="135" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>9</v>
-      </c>
-      <c r="B135">
-        <v>2</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="E135" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="F135" t="s">
+        <v>29</v>
+      </c>
+      <c r="G135" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F135" t="s">
-        <v>29</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136" t="s">
+        <v>368</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D136" s="1" t="s">
+    </row>
+    <row r="137" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>9</v>
-      </c>
-      <c r="B137">
-        <v>2</v>
-      </c>
-      <c r="C137" t="s">
+      <c r="E137" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="F137" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F137" t="s">
-        <v>12</v>
-      </c>
-      <c r="G137" s="1" t="s">
+    </row>
+    <row r="138" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>9</v>
-      </c>
-      <c r="B138">
-        <v>2</v>
-      </c>
-      <c r="C138" t="s">
+      <c r="E138" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="F138" t="s">
+        <v>12</v>
+      </c>
+      <c r="G138" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F138" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="1" t="s">
+    </row>
+    <row r="139" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>9</v>
-      </c>
-      <c r="B139">
-        <v>2</v>
-      </c>
-      <c r="C139" t="s">
+      <c r="E139" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="F139" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
         <v>378</v>
       </c>
-      <c r="F139" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>9</v>
-      </c>
-      <c r="B140">
-        <v>2</v>
-      </c>
-      <c r="C140" t="s">
+      <c r="E140" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="F140" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F140" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="1" t="s">
+    </row>
+    <row r="141" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>9</v>
-      </c>
-      <c r="B141">
-        <v>2</v>
-      </c>
-      <c r="C141" t="s">
+      <c r="E141" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="F141" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F141" t="s">
-        <v>12</v>
-      </c>
-      <c r="G141" s="1" t="s">
+    </row>
+    <row r="142" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>9</v>
-      </c>
-      <c r="B142">
-        <v>2</v>
-      </c>
-      <c r="C142" t="s">
+      <c r="E142" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="F142" t="s">
+        <v>29</v>
+      </c>
+      <c r="G142" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="F142" t="s">
-        <v>29</v>
-      </c>
-      <c r="G142" s="1" t="s">
+    </row>
+    <row r="143" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143">
-        <v>2</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="E143" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="F143" t="s">
+        <v>29</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
         <v>389</v>
       </c>
-      <c r="F143" t="s">
-        <v>29</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>9</v>
-      </c>
-      <c r="B144">
-        <v>2</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="E144" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="F144" t="s">
+        <v>29</v>
+      </c>
+      <c r="G144" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="F144" t="s">
-        <v>29</v>
-      </c>
-      <c r="G144" s="1" t="s">
+    </row>
+    <row r="145" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>9</v>
-      </c>
-      <c r="B145">
-        <v>2</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="E145" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="F145" t="s">
+        <v>29</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
         <v>394</v>
       </c>
-      <c r="F145" t="s">
-        <v>29</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>9</v>
-      </c>
-      <c r="B146">
-        <v>2</v>
-      </c>
-      <c r="C146" t="s">
+      <c r="E146" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="F146" t="s">
         <v>29</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147" t="s">
+        <v>396</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D147" s="1" t="s">
+    </row>
+    <row r="148" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>9</v>
-      </c>
-      <c r="B148">
-        <v>2</v>
-      </c>
-      <c r="C148" t="s">
+      <c r="E148" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="F148" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F148" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="1" t="s">
+    </row>
+    <row r="149" spans="1:7" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="144" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>9</v>
-      </c>
-      <c r="B149">
-        <v>2</v>
-      </c>
-      <c r="C149" t="s">
+      <c r="E149" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="F149" t="s">
+        <v>29</v>
+      </c>
+      <c r="G149" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F149" t="s">
-        <v>29</v>
-      </c>
-      <c r="G149" s="1" t="s">
+    </row>
+    <row r="150" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>9</v>
-      </c>
-      <c r="B150">
-        <v>2</v>
-      </c>
-      <c r="C150" t="s">
+      <c r="E150" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="F150" t="s">
+        <v>29</v>
+      </c>
+      <c r="G150" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="F150" t="s">
-        <v>29</v>
-      </c>
-      <c r="G150" s="1" t="s">
+    </row>
+    <row r="151" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>9</v>
-      </c>
-      <c r="B151">
-        <v>2</v>
-      </c>
-      <c r="C151" t="s">
+      <c r="E151" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>409</v>
-      </c>
       <c r="F151" t="s">
         <v>29</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152" t="s">
+        <v>409</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D152" s="1" t="s">
+    </row>
+    <row r="153" spans="1:7" ht="129.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>9</v>
-      </c>
-      <c r="B153">
-        <v>2</v>
-      </c>
-      <c r="C153" t="s">
+      <c r="E153" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="F153" t="s">
+        <v>29</v>
+      </c>
+      <c r="G153" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F153" t="s">
-        <v>29</v>
-      </c>
-      <c r="G153" s="1" t="s">
+    </row>
+    <row r="154" spans="1:7" ht="158.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154">
+        <v>2</v>
+      </c>
+      <c r="C154" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="158.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>9</v>
-      </c>
-      <c r="B154">
-        <v>2</v>
-      </c>
-      <c r="C154" t="s">
+      <c r="E154" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="F154" t="s">
+        <v>29</v>
+      </c>
+      <c r="G154" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F154" t="s">
-        <v>29</v>
-      </c>
-      <c r="G154" s="1" t="s">
+    </row>
+    <row r="155" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>9</v>
-      </c>
-      <c r="B155">
-        <v>2</v>
-      </c>
-      <c r="C155" t="s">
+      <c r="E155" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="F155" t="s">
+        <v>29</v>
+      </c>
+      <c r="G155" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F155" t="s">
-        <v>29</v>
-      </c>
-      <c r="G155" s="1" t="s">
+    </row>
+    <row r="156" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156">
+        <v>2</v>
+      </c>
+      <c r="C156" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>9</v>
-      </c>
-      <c r="B156">
-        <v>2</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="E156" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="F156" t="s">
         <v>29</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157" t="s">
+        <v>422</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D157" s="1" t="s">
+    </row>
+    <row r="158" spans="1:7" ht="115.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>9</v>
+      </c>
+      <c r="B158">
+        <v>2</v>
+      </c>
+      <c r="C158" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>9</v>
-      </c>
-      <c r="B158">
-        <v>2</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="E158" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="F158" t="s">
+        <v>29</v>
+      </c>
+      <c r="G158" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F158" t="s">
-        <v>29</v>
-      </c>
-      <c r="G158" s="1" t="s">
+    </row>
+    <row r="159" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>9</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>9</v>
-      </c>
-      <c r="B159">
-        <v>2</v>
-      </c>
-      <c r="C159" t="s">
+      <c r="E159" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="E159" s="1" t="s">
+      <c r="F159" t="s">
+        <v>29</v>
+      </c>
+      <c r="G159" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F159" t="s">
-        <v>29</v>
-      </c>
-      <c r="G159" s="1" t="s">
+    </row>
+    <row r="160" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>9</v>
+      </c>
+      <c r="B160">
+        <v>2</v>
+      </c>
+      <c r="C160" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>9</v>
-      </c>
-      <c r="B160">
-        <v>2</v>
-      </c>
-      <c r="C160" t="s">
+      <c r="E160" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="F160" t="s">
+        <v>29</v>
+      </c>
+      <c r="G160" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="F160" t="s">
-        <v>29</v>
-      </c>
-      <c r="G160" s="1" t="s">
+    </row>
+    <row r="161" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>9</v>
+      </c>
+      <c r="B161">
+        <v>2</v>
+      </c>
+      <c r="C161" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>9</v>
-      </c>
-      <c r="B161">
-        <v>2</v>
-      </c>
-      <c r="C161" t="s">
+      <c r="E161" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="E161" s="1" t="s">
+      <c r="F161" t="s">
+        <v>29</v>
+      </c>
+      <c r="G161" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F161" t="s">
-        <v>29</v>
-      </c>
-      <c r="G161" s="1" t="s">
+    </row>
+    <row r="162" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>9</v>
+      </c>
+      <c r="B162">
+        <v>2</v>
+      </c>
+      <c r="C162" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>9</v>
-      </c>
-      <c r="B162">
-        <v>2</v>
-      </c>
-      <c r="C162" t="s">
+      <c r="E162" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E162" s="1" t="s">
+      <c r="F162" t="s">
+        <v>29</v>
+      </c>
+      <c r="G162" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F162" t="s">
-        <v>29</v>
-      </c>
-      <c r="G162" s="1" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163" t="s">
+        <v>439</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D163" s="1" t="s">
+    </row>
+    <row r="164" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>9</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
+      </c>
+      <c r="C164" t="s">
         <v>441</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>9</v>
-      </c>
-      <c r="B164">
-        <v>2</v>
-      </c>
-      <c r="C164" t="s">
+      <c r="E164" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E164" s="1" t="s">
+      <c r="F164" t="s">
+        <v>29</v>
+      </c>
+      <c r="G164" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="F164" t="s">
-        <v>29</v>
-      </c>
-      <c r="G164" s="1" t="s">
+    </row>
+    <row r="165" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>9</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>9</v>
-      </c>
-      <c r="B165">
-        <v>2</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="E165" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="F165" t="s">
+        <v>29</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F165" t="s">
-        <v>29</v>
-      </c>
-      <c r="G165" s="1" t="s">
+    </row>
+    <row r="166" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>9</v>
-      </c>
-      <c r="B166">
-        <v>2</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="E166" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="E166" s="1" t="s">
+      <c r="F166" t="s">
+        <v>29</v>
+      </c>
+      <c r="G166" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="F166" t="s">
-        <v>29</v>
-      </c>
-      <c r="G166" s="1" t="s">
+    </row>
+    <row r="167" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>9</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>9</v>
-      </c>
-      <c r="B167">
-        <v>2</v>
-      </c>
-      <c r="C167" t="s">
+      <c r="E167" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="E167" s="1" t="s">
+      <c r="F167" t="s">
+        <v>29</v>
+      </c>
+      <c r="G167" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="F167" t="s">
-        <v>29</v>
-      </c>
-      <c r="G167" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168" t="s">
+        <v>453</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="D168" s="1" t="s">
+    </row>
+    <row r="169" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169">
+        <v>2</v>
+      </c>
+      <c r="C169" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>9</v>
-      </c>
-      <c r="B169">
-        <v>2</v>
-      </c>
-      <c r="C169" t="s">
+      <c r="E169" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E169" s="1" t="s">
+      <c r="F169" t="s">
+        <v>29</v>
+      </c>
+      <c r="G169" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F169" t="s">
-        <v>29</v>
-      </c>
-      <c r="G169" s="1" t="s">
+    </row>
+    <row r="170" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>9</v>
-      </c>
-      <c r="B170">
-        <v>2</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="E170" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="F170" t="s">
+        <v>29</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" t="s">
         <v>460</v>
       </c>
-      <c r="F170" t="s">
-        <v>29</v>
-      </c>
-      <c r="G170" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>9</v>
-      </c>
-      <c r="B171">
-        <v>2</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="E171" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="E171" s="1" t="s">
+      <c r="F171" t="s">
+        <v>29</v>
+      </c>
+      <c r="G171" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F171" t="s">
-        <v>29</v>
-      </c>
-      <c r="G171" s="1" t="s">
+    </row>
+    <row r="172" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172">
+        <v>2</v>
+      </c>
+      <c r="C172" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>9</v>
-      </c>
-      <c r="B172">
-        <v>2</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="E172" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="E172" s="1" t="s">
+      <c r="F172" t="s">
+        <v>29</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173">
+        <v>2</v>
+      </c>
+      <c r="C173" t="s">
         <v>465</v>
       </c>
-      <c r="F172" t="s">
-        <v>29</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>9</v>
-      </c>
-      <c r="B173">
-        <v>2</v>
-      </c>
-      <c r="C173" t="s">
+      <c r="E173" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E173" s="1" t="s">
+      <c r="F173" t="s">
+        <v>29</v>
+      </c>
+      <c r="G173" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F173" t="s">
-        <v>29</v>
-      </c>
-      <c r="G173" s="1" t="s">
+    </row>
+    <row r="174" spans="1:7" ht="100.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174">
+        <v>2</v>
+      </c>
+      <c r="C174" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>9</v>
-      </c>
-      <c r="B174">
-        <v>2</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="E174" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="E174" s="1" t="s">
+      <c r="F174" t="s">
+        <v>29</v>
+      </c>
+      <c r="G174" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="F174" t="s">
-        <v>29</v>
-      </c>
-      <c r="G174" s="1" t="s">
+    </row>
+    <row r="175" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175">
+        <v>2</v>
+      </c>
+      <c r="C175" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>9</v>
-      </c>
-      <c r="B175">
-        <v>2</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="E175" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="E175" s="1" t="s">
+      <c r="F175" t="s">
+        <v>29</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176">
+        <v>2</v>
+      </c>
+      <c r="C176" t="s">
         <v>473</v>
       </c>
-      <c r="F175" t="s">
-        <v>29</v>
-      </c>
-      <c r="G175" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>9</v>
-      </c>
-      <c r="B176">
-        <v>2</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="E176" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E176" s="1" t="s">
+      <c r="F176" t="s">
+        <v>29</v>
+      </c>
+      <c r="G176" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F176" t="s">
-        <v>29</v>
-      </c>
-      <c r="G176" s="1" t="s">
+    </row>
+    <row r="177" spans="1:7" ht="86.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>9</v>
-      </c>
-      <c r="B177">
-        <v>2</v>
-      </c>
-      <c r="C177" t="s">
+      <c r="E177" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="E177" s="1" t="s">
+      <c r="F177" t="s">
+        <v>29</v>
+      </c>
+      <c r="G177" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F177" t="s">
-        <v>29</v>
-      </c>
-      <c r="G177" s="1" t="s">
+    </row>
+    <row r="178" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178">
+        <v>2</v>
+      </c>
+      <c r="C178" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>9</v>
-      </c>
-      <c r="B178">
-        <v>2</v>
-      </c>
-      <c r="C178" t="s">
+      <c r="E178" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="E178" s="1" t="s">
+      <c r="F178" t="s">
+        <v>29</v>
+      </c>
+      <c r="G178" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="F178" t="s">
-        <v>29</v>
-      </c>
-      <c r="G178" s="1" t="s">
+    </row>
+    <row r="179" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179">
+        <v>2</v>
+      </c>
+      <c r="C179" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>9</v>
-      </c>
-      <c r="B179">
-        <v>2</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="E179" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="E179" s="1" t="s">
+      <c r="F179" t="s">
+        <v>29</v>
+      </c>
+      <c r="G179" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="F179" t="s">
-        <v>29</v>
-      </c>
-      <c r="G179" s="1" t="s">
+    </row>
+    <row r="180" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180">
+        <v>2</v>
+      </c>
+      <c r="C180" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>9</v>
-      </c>
-      <c r="B180">
-        <v>2</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="E180" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E180" s="1" t="s">
+      <c r="F180" t="s">
+        <v>29</v>
+      </c>
+      <c r="G180" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F180" t="s">
-        <v>29</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:7" ht="28.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181" t="s">
+        <v>488</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D181" s="1" t="s">
+    </row>
+    <row r="182" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182">
+        <v>2</v>
+      </c>
+      <c r="C182" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>9</v>
-      </c>
-      <c r="B182">
-        <v>2</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="E182" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="F182" t="s">
+        <v>29</v>
+      </c>
+      <c r="G182" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F182" t="s">
-        <v>29</v>
-      </c>
-      <c r="G182" s="1" t="s">
+    </row>
+    <row r="183" spans="1:7" ht="115.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" ht="115.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>9</v>
-      </c>
-      <c r="B183">
-        <v>2</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="E183" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="F183" t="s">
+        <v>29</v>
+      </c>
+      <c r="G183" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F183" t="s">
-        <v>29</v>
-      </c>
-      <c r="G183" s="1" t="s">
+    </row>
+    <row r="184" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>9</v>
-      </c>
-      <c r="B184">
-        <v>2</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="E184" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="E184" s="1" t="s">
+      <c r="F184" t="s">
+        <v>29</v>
+      </c>
+      <c r="G184" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F184" t="s">
-        <v>29</v>
-      </c>
-      <c r="G184" s="1" t="s">
+    </row>
+    <row r="185" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185">
+        <v>2</v>
+      </c>
+      <c r="C185" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>9</v>
-      </c>
-      <c r="B185">
-        <v>2</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="E185" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="E185" s="1" t="s">
+      <c r="F185" t="s">
+        <v>29</v>
+      </c>
+      <c r="G185" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F185" t="s">
-        <v>29</v>
-      </c>
-      <c r="G185" s="1" t="s">
+    </row>
+    <row r="186" spans="1:7" ht="57.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186">
+        <v>2</v>
+      </c>
+      <c r="C186" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>9</v>
-      </c>
-      <c r="B186">
-        <v>2</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="E186" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="E186" s="1" t="s">
+      <c r="F186" t="s">
+        <v>29</v>
+      </c>
+      <c r="G186" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F186" t="s">
-        <v>29</v>
-      </c>
-      <c r="G186" s="1" t="s">
+    </row>
+    <row r="187" spans="1:7" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>9</v>
-      </c>
-      <c r="B187">
-        <v>2</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="E187" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="E187" s="1" t="s">
+      <c r="F187" t="s">
+        <v>29</v>
+      </c>
+      <c r="G187" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="F187" t="s">
-        <v>29</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -6152,25 +6152,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -6181,13 +6181,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6195,20 +6195,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>533</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -6219,17 +6219,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -6240,26 +6240,26 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
